--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>רני רחמים - עכשיו זה נגמר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a9%d7%a8-%d7%9b%d7%94%d7%9f-%d7%9b%d7%95%d7%9c%d7%9d-%d7%92%d7%a0%d7%91%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410122&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אושר כהן שר דינמיקה זוגית לא בריאה, כמעט ממכרת בשיר פופ ים־תיכוני  שמשלב בין רגש גולמי, דרמה קולית והפקה עכשווית בשיר המתאר מערכת יחסים רעילה בגיל צעיר ליבת השיר היא מערכת יחסים סוערת שמבוססת על משיכה–דחייה: מצד אחד: "אני אוהב</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,430 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>רני רחמים - עכשיו זה נגמר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רגב הוד - תודה לאל קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410121&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רגב הוד - תודה לאל קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתי גדמו - כל מה שבניתי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410120&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתי גדמו - כל מה שבניתי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נהוראי אריאלי - זהות בדויה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410119&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נהוראי אריאלי - זהות בדויה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>לידור - כל מה שעשיתי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410118&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>לידור - כל מה שעשיתי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יותם רכס - עסקים כרגיל</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410117&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יותם רכס - עסקים כרגיל</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בן צור - אישתי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410116&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בן צור - אישתי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אתל - טוקסיק</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410115&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אתל - טוקסיק</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ארי ברמן - דור הגאולה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410114&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ארי ברמן - דור הגאולה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלה הודיה גוילי - סוף העולם</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410113&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלה הודיה גוילי - סוף העולם</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אדל חן - אושר אמיתי</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410112&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אדל חן - אושר אמיתי</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>פו פייטרס Caught In The Echo</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>פו פייטרס Caught In The Echo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410122&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410121&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410120&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410119&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410118&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410117&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410116&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
       <c r="B9" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410115&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410114&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,126 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410113&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410112&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C13" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבי חן - לחזור לבית</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבי חן - לחזור לבית</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
+        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>שירה זלוף - הפסקה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410142&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>שירה זלוף - הפסקה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שיר זוארץ - אוטוטו</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410141&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שיר זוארץ - אוטוטו</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רון פרץ - פול מון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410140&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רון פרץ - פול מון</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410139&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נמואל - יום בא</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410138&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נמואל - יום בא</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מירב ארז - אלף לילה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410137&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מירב ארז - אלף לילה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ליר - לא באמת כואב</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410136&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ליר - לא באמת כואב</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יערה לוי - קיטשי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410135&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יערה לוי - קיטשי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ינון טייב - גור אריה יהודה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410134&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ינון טייב - גור אריה יהודה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוסף ממיה - דרכה של תורה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410133&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוסף ממיה - דרכה של תורה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אביה שרמן - ציון</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410132&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אביה שרמן - ציון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירה זלוף - הפסקה</v>
+        <v>רועי בנטין - ציפורים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410142&amp;sid=0d8343258330d16e696614b7e3125352</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410143&amp;sid=416d2de173a9fe843e6a9b7d81d0dd34</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירה זלוף - הפסקה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שיר זוארץ - אוטוטו</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410141&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שיר זוארץ - אוטוטו</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רון פרץ - פול מון</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410140&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רון פרץ - פול מון</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410139&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נמואל - יום בא</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410138&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נמואל - יום בא</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מירב ארז - אלף לילה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410137&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מירב ארז - אלף לילה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליר - לא באמת כואב</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410136&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליר - לא באמת כואב</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יערה לוי - קיטשי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410135&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יערה לוי - קיטשי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ינון טייב - גור אריה יהודה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410134&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ינון טייב - גור אריה יהודה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יוסף ממיה - דרכה של תורה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410133&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יוסף ממיה - דרכה של תורה</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אביה שרמן - ציון</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410132&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אביה שרמן - ציון</v>
+        <v>רועי בנטין - ציפורים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי בנטין - ציפורים</v>
+        <v>נתלי – השטן לובשת פראדה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410143&amp;sid=416d2de173a9fe843e6a9b7d81d0dd34</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%94%d7%a9%d7%98%d7%9f-%d7%9c%d7%95%d7%91%d7%a9%d7%aa-%d7%a4%d7%a8%d7%90%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“השטן לובשת פראדה” של נתלי הוא פופ עכשווי שמצליח להיות גם קליט וגם טעון, ומה שמעניין בו  הוא הפער בין המעטפת הזוהרת לבין תוכן רגשי כבד, כמעט קיומי. שם השיר כמובן מהדהד את The Devil Wears Prada, אבל כאן “פראדה”</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי בנטין - ציפורים</v>
+        <v>נתלי – השטן לובשת פראדה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתלי – השטן לובשת פראדה</v>
+        <v>אודיה – שיר לממ"ד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%94%d7%a9%d7%98%d7%9f-%d7%9c%d7%95%d7%91%d7%a9%d7%aa-%d7%a4%d7%a8%d7%90%d7%93%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99%d7%94-%d7%a9%d7%99%d7%a8-%d7%9c%d7%9e%d7%9e%d7%93/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“השטן לובשת פראדה” של נתלי הוא פופ עכשווי שמצליח להיות גם קליט וגם טעון, ומה שמעניין בו  הוא הפער בין המעטפת הזוהרת לבין תוכן רגשי כבד, כמעט קיומי. שם השיר כמובן מהדהד את The Devil Wears Prada, אבל כאן “פראדה”</v>
+        <v>אודיה שרה שיר שהוא ניסיון מובהק ליצור שיר “של הדור” – כזה שמחבר שמות, סיטואציות וסלנג לכדי קולאז’ חברת, אבל בין הכוונה לייצר אמירה רחבה לבין הביצוע, נוצר פער לא קטן. השיר בנוי כרצף דמויות: ששון, אלינור, שלום, רוקי, אורי,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתלי – השטן לובשת פראדה</v>
+        <v>אודיה – שיר לממ"ד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אודיה – שיר לממ"ד</v>
+        <v>הודיה ויצמן - עכשיו בסדר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99%d7%94-%d7%a9%d7%99%d7%a8-%d7%9c%d7%9e%d7%9e%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410149&amp;sid=8b258206d76373ed616ca34a422be80f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אודיה שרה שיר שהוא ניסיון מובהק ליצור שיר “של הדור” – כזה שמחבר שמות, סיטואציות וסלנג לכדי קולאז’ חברת, אבל בין הכוונה לייצר אמירה רחבה לבין הביצוע, נוצר פער לא קטן. השיר בנוי כרצף דמויות: ששון, אלינור, שלום, רוקי, אורי,</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,164 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אודיה – שיר לממ"ד</v>
+        <v>הודיה ויצמן - עכשיו בסדר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אפיק מרחום - איתך הייתי פורח</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410148&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אפיק מרחום - איתך הייתי פורח</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אלי וינר - אף פעם לא לבד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410147&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אלי וינר - אף פעם לא לבד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אופק יפרח אזולאי - עלם חמודות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410146&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אופק יפרח אזולאי - עלם חמודות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אודיה - שיר לממ"ד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410145&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אודיה - שיר לממ"ד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הודיה ויצמן - עכשיו בסדר</v>
+        <v>יוסי פריד - עבדים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410149&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410153&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הודיה ויצמן - עכשיו בסדר</v>
+        <v>יוסי פריד - עבדים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אפיק מרחום - איתך הייתי פורח</v>
+        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410148&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410152&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אפיק מרחום - איתך הייתי פורח</v>
+        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלי וינר - אף פעם לא לבד</v>
+        <v>יהודה נר - כמה טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410147&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410151&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלי וינר - אף פעם לא לבד</v>
+        <v>יהודה נר - כמה טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אופק יפרח אזולאי - עלם חמודות</v>
+        <v>טוני ג'ינו - נשמה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410146&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410150&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-24</v>
@@ -583,50 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אופק יפרח אזולאי - עלם חמודות</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אודיה - שיר לממ"ד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410145&amp;sid=8b258206d76373ed616ca34a422be80f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אודיה - שיר לממ"ד</v>
+        <v>טוני ג'ינו - נשמה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוסי פריד - עבדים</v>
+        <v>רויטל נחמני - מחרוזת אש 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410153&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410164&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוסי פריד - עבדים</v>
+        <v>רויטל נחמני - מחרוזת אש 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
+        <v>ששון שאולוב - ציון</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410152&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410163&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
+        <v>ששון שאולוב - ציון</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יהודה נר - כמה טוב</v>
+        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410151&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410162&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יהודה נר - כמה טוב</v>
+        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טוני ג'ינו - נשמה</v>
+        <v>שלום ממן - יא בנתי בלאדי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410150&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410161&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-24</v>
@@ -583,12 +583,278 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טוני ג'ינו - נשמה</v>
+        <v>שלום ממן - יא בנתי בלאדי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רועי אדרי - תבואי אליי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410160&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רועי אדרי - תבואי אליי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410159&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>קובי פרץ - הלב לא שוכח</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410158&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>קובי פרץ - הלב לא שוכח</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>עמנואל זאודה - תשמור עליי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410157&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>עמנואל זאודה - תשמור עליי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410156&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>נעם ישראל - סטלה ברומו</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410155&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>נעם ישראל - סטלה ברומו</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>משה כורסיה - דגל על הגב</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410154&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>משה כורסיה - דגל על הגב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רויטל נחמני - מחרוזת אש 2026</v>
+        <v>ששון שאולוב – ציון</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410164&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a6%d7%99%d7%95%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"ציון" של אליעזר בוצר הוא לא “שיר מרגש” במובן הפשוט של המילה. זה טקסט פיוטי-רוחני-לאומי כמעט נבואי. הוא נע בין אהבה לציון (כישות כמעט נשית) אשמה, חטא, ותשובה, חיפוש גאולה אישית וקולקטיבית, שיר שיש בו כאב, אבל גם עוצמה ואש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רויטל נחמני - מחרוזת אש 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ששון שאולוב - ציון</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410163&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ששון שאולוב - ציון</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410162&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שלום ממן - יא בנתי בלאדי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410161&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שלום ממן - יא בנתי בלאדי</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>רועי אדרי - תבואי אליי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410160&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>רועי אדרי - תבואי אליי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מיכאל בן שבת - דלת לליבך 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410159&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מיכאל בן שבת - דלת לליבך 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>קובי פרץ - הלב לא שוכח</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410158&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>קובי פרץ - הלב לא שוכח</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>עמנואל זאודה - תשמור עליי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410157&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>עמנואל זאודה - תשמור עליי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410156&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>נעם ישראל - סטלה ברומו</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410155&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>נעם ישראל - סטלה ברומו</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>משה כורסיה - דגל על הגב</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410154&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>משה כורסיה - דגל על הגב</v>
+        <v>ששון שאולוב – ציון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב – ציון</v>
+        <v>שמעון גרשון - זה הלב שלך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a6%d7%99%d7%95%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410180&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ציון" של אליעזר בוצר הוא לא “שיר מרגש” במובן הפשוט של המילה. זה טקסט פיוטי-רוחני-לאומי כמעט נבואי. הוא נע בין אהבה לציון (כישות כמעט נשית) אשמה, חטא, ותשובה, חיפוש גאולה אישית וקולקטיבית, שיר שיש בו כאב, אבל גם עוצמה ואש</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,544 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב – ציון</v>
+        <v>שמעון גרשון - זה הלב שלך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רינת בר - נפש תאומה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410179&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רינת בר - נפש תאומה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עתרת - געגוע</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410178&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עתרת - געגוע</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410177&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נר &amp; נתן - תמיד איתך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410176&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נר &amp; נתן - תמיד איתך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410175&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יוחאי בן אב''י - אהבת עולם</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410174&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יוחאי בן אב''י - אהבת עולם</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יהודה יפרח - מקום חדש</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410173&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יהודה יפרח - מקום חדש</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410172&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410171&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>בן צור - יש אמת אחת</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410169&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>בן צור - יש אמת אחת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלקנה אלפסי - לברוח ממני</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410168&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלקנה אלפסי - לברוח ממני</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איציק שריקי - מאושרת לעולם</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410167&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איציק שריקי - מאושרת לעולם</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410166&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410165&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון ומתן לוי – עושה שלום</v>
+        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%95%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a9%d7%9c%d7%95%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410189&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "עושה שלום" בביצוע של עדן חסון ומתן לוי הוא ניסיון לגעת במקום רוחני־רגשי רחב, כזה שמחבר בין תפילה יהודית, פופ עכשווי, ואווירה של נחמה אחרי משבר. זה שיר שמכוון גבוה, לשאלות של אמונה, תקווה ומשמעות, אבל עושה זאת דרך</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון ומתן לוי – עושה שלום</v>
+        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רון יוסף - גבר אמיתי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410188&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רון יוסף - גבר אמיתי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קובי אפללו - שיר של אהבה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410187&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קובי אפללו - שיר של אהבה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410186&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410185&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>היוצרים - אבא</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410184&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>היוצרים - אבא</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410183&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אליאור זנדני - מיליון מילים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410182&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אליאור זנדני - מיליון מילים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אודי צברי - אין לי יום</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410181&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אודי צברי - אין לי יום</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
+        <v>שי חזן - מחרוזת שנות ה 90 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410189&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410204&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
+        <v>שי חזן - מחרוזת שנות ה 90 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון יוסף - גבר אמיתי</v>
+        <v>רפאל מלול - בכל דור ודור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410188&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410203&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון יוסף - גבר אמיתי</v>
+        <v>רפאל מלול - בכל דור ודור קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קובי אפללו - שיר של אהבה</v>
+        <v>פינחס מלך כהן - חלק ממך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410187&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410202&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קובי אפללו - שיר של אהבה</v>
+        <v>פינחס מלך כהן - חלק ממך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+        <v>נשמה וקצב - החצי שלך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410186&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410201&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+        <v>נשמה וקצב - החצי שלך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+        <v>נועם צוריאלי - צאי כבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410185&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410200&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+        <v>נועם צוריאלי - צאי כבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>היוצרים - אבא</v>
+        <v>חביב שאשא - שאת הולכת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410184&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410199&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>היוצרים - אבא</v>
+        <v>חביב שאשא - שאת הולכת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+        <v>מאיה דדון &amp; גולדבאום - מה נשתנה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410183&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410198&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+        <v>מאיה דדון &amp; גולדבאום - מה נשתנה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אליאור זנדני - מיליון מילים</v>
+        <v>יהודה אביאל - מחרוזת מאוהב בגשם 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410182&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410197&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אליאור זנדני - מיליון מילים</v>
+        <v>יהודה אביאל - מחרוזת מאוהב בגשם 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אודי צברי - אין לי יום</v>
+        <v>מאי קריטי &amp; אלי בן חמו - מחרוזת פעם בחיים 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410181&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410196&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,12 +773,202 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אודי צברי - אין לי יום</v>
+        <v>מאי קריטי &amp; אלי בן חמו - מחרוזת פעם בחיים 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יניב בן ישי - רואה אותך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410195&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יניב בן ישי - רואה אותך</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חן אלדטוב - קפה שחור</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410194&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חן אלדטוב - קפה שחור</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>היוצרים - אל תגיד אוף תגיד פרק ק</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410193&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>היוצרים - אל תגיד אוף תגיד פרק ק</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אדיר אליה - אין לנו יותר סיכוי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410192&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אדיר אליה - אין לנו יותר סיכוי</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את ביני לנדאו - יְדִיד נֶפֶשׁ</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410191&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את ביני לנדאו - יְדִיד נֶפֶשׁ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>